--- a/approval_forms/015_software_approval_form--approval_forms.xlsx
+++ b/approval_forms/015_software_approval_form--approval_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'approved',_'label':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'approved', 'label': 'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'declined',_'label':_'declined'}</t>
+          <t>declined</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'declined', 'label': 'declined'}</t>
+          <t>declined</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'pending',_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'pending', 'label': 'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'requestor1',_'label':_'requestor_1'}</t>
+          <t>requestor_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'requestor1', 'label': 'requestor 1'}</t>
+          <t>requestor 1</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'requestor2',_'label':_'requestor_2'}</t>
+          <t>requestor_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'requestor2', 'label': 'requestor 2'}</t>
+          <t>requestor 2</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'requestor3',_'label':_'requestor_3'}</t>
+          <t>requestor_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'requestor3', 'label': 'requestor 3'}</t>
+          <t>requestor 3</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'reviewer1',_'label':_'reviewer_1'}</t>
+          <t>reviewer_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'reviewer1', 'label': 'reviewer 1'}</t>
+          <t>reviewer 1</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'reviewer2',_'label':_'reviewer_2'}</t>
+          <t>reviewer_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'reviewer2', 'label': 'reviewer 2'}</t>
+          <t>reviewer 2</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'reviewer3',_'label':_'reviewer_3'}</t>
+          <t>reviewer_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'reviewer3', 'label': 'reviewer 3'}</t>
+          <t>reviewer 3</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'version1',_'label':_'version_1'}</t>
+          <t>version_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'version1', 'label': 'version 1'}</t>
+          <t>version 1</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'version2',_'label':_'version_2'}</t>
+          <t>version_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'version2', 'label': 'version 2'}</t>
+          <t>version 2</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'version3',_'label':_'version_3'}</t>
+          <t>version_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'version3', 'label': 'version 3'}</t>
+          <t>version 3</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'implemented',_'label':_'implemented'}</t>
+          <t>implemented</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'implemented', 'label': 'implemented'}</t>
+          <t>implemented</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'not_implemented',_'label':_'not_implemented'}</t>
+          <t>not_implemented</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'not implemented', 'label': 'not implemented'}</t>
+          <t>not implemented</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'pending',_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'pending', 'label': 'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'n/a',_'label':_'n/a'}</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'n/a', 'label': 'n/a'}</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'reviewed',_'label':_'reviewed'}</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'reviewed', 'label': 'reviewed'}</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'not_reviewed',_'label':_'not_reviewed'}</t>
+          <t>not_reviewed</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'not reviewed', 'label': 'not reviewed'}</t>
+          <t>not reviewed</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'n/a',_'label':_'n/a'}</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'n/a', 'label': 'n/a'}</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
